--- a/public/sim2-data/Round3_NewMonth_RawFeed.xlsx
+++ b/public/sim2-data/Round3_NewMonth_RawFeed.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13-04-2026-Notebook Set-249-2</t>
+          <t>46125-Notebook Set-249-2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>08-04-2026-USB-C Hub-999-2</t>
+          <t>46120-USB-C Hub-999-2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -469,7 +469,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24-04-2026-Notebook Set-249-5</t>
+          <t>46136-Notebook Set-249-5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20-04-2026-Whiteboard-1599-2</t>
+          <t>46132-Whiteboard-1599-2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26-04-2026-Office Chair-6499-4</t>
+          <t>46138-Office Chair-6499-4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>05-04-2026-Whiteboard-1599-2</t>
+          <t>46117-Whiteboard-1599-2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>03-04-2026-Webcam HD-2199-1</t>
+          <t>46115-Webcam HD-2199-1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13-04-2026-Wireless Mouse-799-3</t>
+          <t>46125-Wireless Mouse-799-3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14-04-2026-USB-C Hub-999-3</t>
+          <t>46126-USB-C Hub-999-3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15-04-2026-Webcam HD-2199-2</t>
+          <t>46127-Webcam HD-2199-2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>02-04-2026-Office Chair-6499-2</t>
+          <t>46114-Office Chair-6499-2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>24-04-2026-Whiteboard-1599-5</t>
+          <t>46136-Whiteboard-1599-5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>02-04-2026-Laptop Charger-1299-1</t>
+          <t>46114-Laptop Charger-1299-1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22-04-2026-Notebook Set-249-1</t>
+          <t>46134-Notebook Set-249-1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>05-04-2026-Desk Lamp-699-5</t>
+          <t>46117-Desk Lamp-699-5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11-04-2026-Bluetooth Speaker-1899-5</t>
+          <t>46123-Bluetooth Speaker-1899-5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>26-04-2026-Wireless Mouse-799-2</t>
+          <t>46138-Wireless Mouse-799-2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18-04-2026-Notebook Set-249-2</t>
+          <t>46130-Notebook Set-249-2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>02-04-2026-Bluetooth Speaker-1899-5</t>
+          <t>46114-Bluetooth Speaker-1899-5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20-04-2026-Notebook Set-249-1</t>
+          <t>46132-Notebook Set-249-1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>05-04-2026-Desk Lamp-699-2</t>
+          <t>46117-Desk Lamp-699-2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>05-04-2026-USB-C Hub-999-5</t>
+          <t>46117-USB-C Hub-999-5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>26-04-2026-USB-C Hub-999-3</t>
+          <t>46138-USB-C Hub-999-3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>06-04-2026-Laptop Charger-1299-5</t>
+          <t>46118-Laptop Charger-1299-5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19-04-2026-Wireless Mouse-799-3</t>
+          <t>46131-Wireless Mouse-799-3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13-04-2026-Office Chair-6499-4</t>
+          <t>46125-Office Chair-6499-4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>27-04-2026-Office Chair-6499-5</t>
+          <t>46139-Office Chair-6499-5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>02-04-2026-Office Chair-6499-4</t>
+          <t>46114-Office Chair-6499-4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10-04-2026-USB-C Hub-999-3</t>
+          <t>46122-USB-C Hub-999-3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>07-04-2026-USB-C Hub-999-4</t>
+          <t>46119-USB-C Hub-999-4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>25-04-2026-Laptop Charger-1299-4</t>
+          <t>46137-Laptop Charger-1299-4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>03-04-2026-Webcam HD-2199-3</t>
+          <t>46115-Webcam HD-2199-3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>26-04-2026-Whiteboard-1599-5</t>
+          <t>46138-Whiteboard-1599-5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14-04-2026-Desk Lamp-699-4</t>
+          <t>46126-Desk Lamp-699-4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10-04-2026-Notebook Set-249-5</t>
+          <t>46122-Notebook Set-249-5</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>07-04-2026-Notebook Set-249-3</t>
+          <t>46119-Notebook Set-249-3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01-04-2026-Office Chair-6499-3</t>
+          <t>46113-Office Chair-6499-3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>26-04-2026-Desk Lamp-699-4</t>
+          <t>46138-Desk Lamp-699-4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14-04-2026-Office Chair-6499-4</t>
+          <t>46126-Office Chair-6499-4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17-04-2026-Webcam HD-2199-2</t>
+          <t>46129-Webcam HD-2199-2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>22-04-2026-Bluetooth Speaker-1899-5</t>
+          <t>46134-Bluetooth Speaker-1899-5</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>09-04-2026-Notebook Set-249-4</t>
+          <t>46121-Notebook Set-249-4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>07-04-2026-Wireless Mouse-799-1</t>
+          <t>46119-Wireless Mouse-799-1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>19-04-2026-Wireless Mouse-799-1</t>
+          <t>46131-Wireless Mouse-799-1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12-04-2026-Webcam HD-2199-5</t>
+          <t>46124-Webcam HD-2199-5</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>07-04-2026-Laptop Charger-1299-4</t>
+          <t>46119-Laptop Charger-1299-4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>09-04-2026-Whiteboard-1599-3</t>
+          <t>46121-Whiteboard-1599-3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15-04-2026-Notebook Set-249-4</t>
+          <t>46127-Notebook Set-249-4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12-04-2026-Desk Lamp-699-2</t>
+          <t>46124-Desk Lamp-699-2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19-04-2026-Notebook Set-249-2</t>
+          <t>46131-Notebook Set-249-2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22-04-2026-Bluetooth Speaker-1899-1</t>
+          <t>46134-Bluetooth Speaker-1899-1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15-04-2026-Webcam HD-2199-1</t>
+          <t>46127-Webcam HD-2199-1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>26-04-2026-Whiteboard-1599-1</t>
+          <t>46138-Whiteboard-1599-1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>19-04-2026-Webcam HD-2199-3</t>
+          <t>46131-Webcam HD-2199-3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>19-04-2026-Office Chair-6499-4</t>
+          <t>46131-Office Chair-6499-4</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>05-04-2026-Mechanical Keyboard-3299-1</t>
+          <t>46117-Mechanical Keyboard-3299-1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>02-04-2026-Office Chair-6499-5</t>
+          <t>46114-Office Chair-6499-5</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>06-04-2026-Whiteboard-1599-1</t>
+          <t>46118-Whiteboard-1599-1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>08-04-2026-USB-C Hub-999-1</t>
+          <t>46120-USB-C Hub-999-1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>09-04-2026-Desk Lamp-699-3</t>
+          <t>46121-Desk Lamp-699-3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>25-04-2026-Webcam HD-2199-2</t>
+          <t>46137-Webcam HD-2199-2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21-04-2026-Webcam HD-2199-1</t>
+          <t>46133-Webcam HD-2199-1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>24-04-2026-Bluetooth Speaker-1899-2</t>
+          <t>46136-Bluetooth Speaker-1899-2</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>02-04-2026-Webcam HD-2199-4</t>
+          <t>46114-Webcam HD-2199-4</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>28-04-2026-USB-C Hub-999-5</t>
+          <t>46140-USB-C Hub-999-5</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11-04-2026-Wireless Mouse-799-3</t>
+          <t>46123-Wireless Mouse-799-3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>07-04-2026-Desk Lamp-699-2</t>
+          <t>46119-Desk Lamp-699-2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>05-04-2026-Whiteboard-1599-5</t>
+          <t>46117-Whiteboard-1599-5</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>08-04-2026-Notebook Set-249-1</t>
+          <t>46120-Notebook Set-249-1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>24-04-2026-Mechanical Keyboard-3299-1</t>
+          <t>46136-Mechanical Keyboard-3299-1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>25-04-2026-Whiteboard-1599-3</t>
+          <t>46137-Whiteboard-1599-3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>19-04-2026-Wireless Mouse-799-5</t>
+          <t>46131-Wireless Mouse-799-5</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>10-04-2026-Bluetooth Speaker-1899-2</t>
+          <t>46122-Bluetooth Speaker-1899-2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>26-04-2026-Webcam HD-2199-3</t>
+          <t>46138-Webcam HD-2199-3</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>16-04-2026-Notebook Set-249-1</t>
+          <t>46128-Notebook Set-249-1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>06-04-2026-Mechanical Keyboard-3299-3</t>
+          <t>46118-Mechanical Keyboard-3299-3</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>26-04-2026-Wireless Mouse-799-4</t>
+          <t>46138-Wireless Mouse-799-4</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>18-04-2026-Bluetooth Speaker-1899-1</t>
+          <t>46130-Bluetooth Speaker-1899-1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>14-04-2026-Webcam HD-2199-2</t>
+          <t>46126-Webcam HD-2199-2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>02-04-2026-USB-C Hub-999-2</t>
+          <t>46114-USB-C Hub-999-2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>06-04-2026-Mechanical Keyboard-3299-1</t>
+          <t>46118-Mechanical Keyboard-3299-1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>19-04-2026-Wireless Mouse-799-2</t>
+          <t>46131-Wireless Mouse-799-2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>21-04-2026-Desk Lamp-699-1</t>
+          <t>46133-Desk Lamp-699-1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>19-04-2026-Notebook Set-249-2</t>
+          <t>46131-Notebook Set-249-2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>17-04-2026-Notebook Set-249-4</t>
+          <t>46129-Notebook Set-249-4</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>19-04-2026-USB-C Hub-999-3</t>
+          <t>46131-USB-C Hub-999-3</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>16-04-2026-Mechanical Keyboard-3299-1</t>
+          <t>46128-Mechanical Keyboard-3299-1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>08-04-2026-Mechanical Keyboard-3299-4</t>
+          <t>46120-Mechanical Keyboard-3299-4</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>14-04-2026-Mechanical Keyboard-3299-2</t>
+          <t>46126-Mechanical Keyboard-3299-2</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>16-04-2026-USB-C Hub-999-2</t>
+          <t>46128-USB-C Hub-999-2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
